--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -5669,25 +5669,25 @@
         <v>46283</v>
       </c>
       <c r="B203" t="n">
-        <v>331500</v>
+        <v>327000</v>
       </c>
       <c r="C203" t="n">
-        <v>21400</v>
+        <v>44047</v>
       </c>
       <c r="D203" t="n">
-        <v>378190</v>
+        <v>377733</v>
       </c>
       <c r="E203" t="n">
-        <v>372697</v>
+        <v>372054</v>
       </c>
       <c r="F203" t="n">
-        <v>330827</v>
+        <v>329559</v>
       </c>
       <c r="G203" t="n">
-        <v>360571</v>
+        <v>359782</v>
       </c>
       <c r="H203" t="n">
-        <v>-0.4218792839448769</v>
+        <v>-0.4231443253513336</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5690,6 +5690,32 @@
         <v>-0.4231443253513336</v>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B204" t="n">
+        <v>327000</v>
+      </c>
+      <c r="C204" t="n">
+        <v>26202</v>
+      </c>
+      <c r="D204" t="n">
+        <v>377319</v>
+      </c>
+      <c r="E204" t="n">
+        <v>371907</v>
+      </c>
+      <c r="F204" t="n">
+        <v>328826</v>
+      </c>
+      <c r="G204" t="n">
+        <v>359351</v>
+      </c>
+      <c r="H204" t="n">
+        <v>-0.4238353682489037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -5721,25 +5721,25 @@
         <v>46287</v>
       </c>
       <c r="B205" t="n">
-        <v>334000</v>
+        <v>331500</v>
       </c>
       <c r="C205" t="n">
-        <v>2900</v>
+        <v>31274</v>
       </c>
       <c r="D205" t="n">
-        <v>377345</v>
+        <v>376858</v>
       </c>
       <c r="E205" t="n">
-        <v>371837</v>
+        <v>371113</v>
       </c>
       <c r="F205" t="n">
-        <v>328047</v>
+        <v>328685</v>
       </c>
       <c r="G205" t="n">
-        <v>359076</v>
+        <v>358885</v>
       </c>
       <c r="H205" t="n">
-        <v>-0.4242762888912048</v>
+        <v>-0.4245825283191303</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5742,6 +5742,32 @@
         <v>-0.4245825283191303</v>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B206" t="n">
+        <v>330000</v>
+      </c>
+      <c r="C206" t="n">
+        <v>22986</v>
+      </c>
+      <c r="D206" t="n">
+        <v>376411</v>
+      </c>
+      <c r="E206" t="n">
+        <v>370527</v>
+      </c>
+      <c r="F206" t="n">
+        <v>329166</v>
+      </c>
+      <c r="G206" t="n">
+        <v>358701</v>
+      </c>
+      <c r="H206" t="n">
+        <v>-0.4248775443125246</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H206"/>
+  <dimension ref="A1:H207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5768,6 +5768,32 @@
         <v>-0.4248775443125246</v>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B207" t="n">
+        <v>332000</v>
+      </c>
+      <c r="C207" t="n">
+        <v>25837</v>
+      </c>
+      <c r="D207" t="n">
+        <v>375709</v>
+      </c>
+      <c r="E207" t="n">
+        <v>369017</v>
+      </c>
+      <c r="F207" t="n">
+        <v>329254</v>
+      </c>
+      <c r="G207" t="n">
+        <v>357993</v>
+      </c>
+      <c r="H207" t="n">
+        <v>-0.4260127145479762</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H207"/>
+  <dimension ref="A1:H208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5794,6 +5794,32 @@
         <v>-0.4260127145479762</v>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B208" t="n">
+        <v>339500</v>
+      </c>
+      <c r="C208" t="n">
+        <v>35830</v>
+      </c>
+      <c r="D208" t="n">
+        <v>375874</v>
+      </c>
+      <c r="E208" t="n">
+        <v>368274</v>
+      </c>
+      <c r="F208" t="n">
+        <v>332535</v>
+      </c>
+      <c r="G208" t="n">
+        <v>358894</v>
+      </c>
+      <c r="H208" t="n">
+        <v>-0.4245680981890186</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H208"/>
+  <dimension ref="A1:H209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5820,6 +5820,32 @@
         <v>-0.4245680981890186</v>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B209" t="n">
+        <v>346000</v>
+      </c>
+      <c r="C209" t="n">
+        <v>45176</v>
+      </c>
+      <c r="D209" t="n">
+        <v>375864</v>
+      </c>
+      <c r="E209" t="n">
+        <v>345232</v>
+      </c>
+      <c r="F209" t="n">
+        <v>337211</v>
+      </c>
+      <c r="G209" t="n">
+        <v>352769</v>
+      </c>
+      <c r="H209" t="n">
+        <v>-0.4343886034039074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H209"/>
+  <dimension ref="A1:H211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5846,6 +5846,58 @@
         <v>-0.4343886034039074</v>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B210" t="n">
+        <v>373500</v>
+      </c>
+      <c r="C210" t="n">
+        <v>94635</v>
+      </c>
+      <c r="D210" t="n">
+        <v>375777</v>
+      </c>
+      <c r="E210" t="n">
+        <v>346743</v>
+      </c>
+      <c r="F210" t="n">
+        <v>353307</v>
+      </c>
+      <c r="G210" t="n">
+        <v>358609</v>
+      </c>
+      <c r="H210" t="n">
+        <v>-0.4250250523092216</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B211" t="n">
+        <v>365000</v>
+      </c>
+      <c r="C211" t="n">
+        <v>24479</v>
+      </c>
+      <c r="D211" t="n">
+        <v>375675</v>
+      </c>
+      <c r="E211" t="n">
+        <v>345959</v>
+      </c>
+      <c r="F211" t="n">
+        <v>356944</v>
+      </c>
+      <c r="G211" t="n">
+        <v>359526</v>
+      </c>
+      <c r="H211" t="n">
+        <v>-0.4235547823856212</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H211"/>
+  <dimension ref="A1:H212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5898,6 +5898,32 @@
         <v>-0.4235547823856212</v>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B212" t="n">
+        <v>371500</v>
+      </c>
+      <c r="C212" t="n">
+        <v>28589</v>
+      </c>
+      <c r="D212" t="n">
+        <v>374937</v>
+      </c>
+      <c r="E212" t="n">
+        <v>346062</v>
+      </c>
+      <c r="F212" t="n">
+        <v>361582</v>
+      </c>
+      <c r="G212" t="n">
+        <v>360860</v>
+      </c>
+      <c r="H212" t="n">
+        <v>-0.4214159164335132</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H212"/>
+  <dimension ref="A1:H213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5924,6 +5924,32 @@
         <v>-0.4214159164335132</v>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B213" t="n">
+        <v>369000</v>
+      </c>
+      <c r="C213" t="n">
+        <v>24304</v>
+      </c>
+      <c r="D213" t="n">
+        <v>374386</v>
+      </c>
+      <c r="E213" t="n">
+        <v>346342</v>
+      </c>
+      <c r="F213" t="n">
+        <v>366055</v>
+      </c>
+      <c r="G213" t="n">
+        <v>362261</v>
+      </c>
+      <c r="H213" t="n">
+        <v>-0.4191696261794627</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H213"/>
+  <dimension ref="A1:H214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5950,6 +5950,32 @@
         <v>-0.4191696261794627</v>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B214" t="n">
+        <v>340500</v>
+      </c>
+      <c r="C214" t="n">
+        <v>44613</v>
+      </c>
+      <c r="D214" t="n">
+        <v>373786</v>
+      </c>
+      <c r="E214" t="n">
+        <v>345710</v>
+      </c>
+      <c r="F214" t="n">
+        <v>364974</v>
+      </c>
+      <c r="G214" t="n">
+        <v>361490</v>
+      </c>
+      <c r="H214" t="n">
+        <v>-0.4204058073256961</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H214"/>
+  <dimension ref="A1:H215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5976,6 +5976,32 @@
         <v>-0.4204058073256961</v>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B215" t="n">
+        <v>325000</v>
+      </c>
+      <c r="C215" t="n">
+        <v>31169</v>
+      </c>
+      <c r="D215" t="n">
+        <v>371200</v>
+      </c>
+      <c r="E215" t="n">
+        <v>344565</v>
+      </c>
+      <c r="F215" t="n">
+        <v>351571</v>
+      </c>
+      <c r="G215" t="n">
+        <v>355779</v>
+      </c>
+      <c r="H215" t="n">
+        <v>-0.4295625265554478</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H215"/>
+  <dimension ref="A1:H216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6002,6 +6002,32 @@
         <v>-0.4295625265554478</v>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B216" t="n">
+        <v>314500</v>
+      </c>
+      <c r="C216" t="n">
+        <v>52694</v>
+      </c>
+      <c r="D216" t="n">
+        <v>369311</v>
+      </c>
+      <c r="E216" t="n">
+        <v>342059</v>
+      </c>
+      <c r="F216" t="n">
+        <v>338988</v>
+      </c>
+      <c r="G216" t="n">
+        <v>350119</v>
+      </c>
+      <c r="H216" t="n">
+        <v>-0.4386374750479</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H216"/>
+  <dimension ref="A1:H217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6028,6 +6028,32 @@
         <v>-0.4386374750479</v>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B217" t="n">
+        <v>309500</v>
+      </c>
+      <c r="C217" t="n">
+        <v>23294</v>
+      </c>
+      <c r="D217" t="n">
+        <v>366734</v>
+      </c>
+      <c r="E217" t="n">
+        <v>341482</v>
+      </c>
+      <c r="F217" t="n">
+        <v>329808</v>
+      </c>
+      <c r="G217" t="n">
+        <v>346008</v>
+      </c>
+      <c r="H217" t="n">
+        <v>-0.4452288378133543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H217"/>
+  <dimension ref="A1:H218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6054,6 +6054,32 @@
         <v>-0.4452288378133543</v>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B218" t="n">
+        <v>305000</v>
+      </c>
+      <c r="C218" t="n">
+        <v>38198</v>
+      </c>
+      <c r="D218" t="n">
+        <v>365764</v>
+      </c>
+      <c r="E218" t="n">
+        <v>339617</v>
+      </c>
+      <c r="F218" t="n">
+        <v>319805</v>
+      </c>
+      <c r="G218" t="n">
+        <v>341729</v>
+      </c>
+      <c r="H218" t="n">
+        <v>-0.4520895630075598</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H218"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6080,6 +6080,32 @@
         <v>-0.4520895630075598</v>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B219" t="n">
+        <v>331500</v>
+      </c>
+      <c r="C219" t="n">
+        <v>56085</v>
+      </c>
+      <c r="D219" t="n">
+        <v>364992</v>
+      </c>
+      <c r="E219" t="n">
+        <v>339366</v>
+      </c>
+      <c r="F219" t="n">
+        <v>318478</v>
+      </c>
+      <c r="G219" t="n">
+        <v>340945</v>
+      </c>
+      <c r="H219" t="n">
+        <v>-0.4533465876750655</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H219"/>
+  <dimension ref="A1:H220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6106,6 +6106,32 @@
         <v>-0.4533465876750655</v>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B220" t="n">
+        <v>350500</v>
+      </c>
+      <c r="C220" t="n">
+        <v>33263</v>
+      </c>
+      <c r="D220" t="n">
+        <v>363788</v>
+      </c>
+      <c r="E220" t="n">
+        <v>340993</v>
+      </c>
+      <c r="F220" t="n">
+        <v>322713</v>
+      </c>
+      <c r="G220" t="n">
+        <v>342498</v>
+      </c>
+      <c r="H220" t="n">
+        <v>-0.4508565885569068</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6132,6 +6132,32 @@
         <v>-0.4508565885569068</v>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B221" t="n">
+        <v>329000</v>
+      </c>
+      <c r="C221" t="n">
+        <v>27672</v>
+      </c>
+      <c r="D221" t="n">
+        <v>362835</v>
+      </c>
+      <c r="E221" t="n">
+        <v>340495</v>
+      </c>
+      <c r="F221" t="n">
+        <v>326112</v>
+      </c>
+      <c r="G221" t="n">
+        <v>343147</v>
+      </c>
+      <c r="H221" t="n">
+        <v>-0.4498160158410762</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H221"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6158,6 +6158,32 @@
         <v>-0.4498160158410762</v>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B222" t="n">
+        <v>335000</v>
+      </c>
+      <c r="C222" t="n">
+        <v>28807</v>
+      </c>
+      <c r="D222" t="n">
+        <v>362567</v>
+      </c>
+      <c r="E222" t="n">
+        <v>340787</v>
+      </c>
+      <c r="F222" t="n">
+        <v>329606</v>
+      </c>
+      <c r="G222" t="n">
+        <v>344320</v>
+      </c>
+      <c r="H222" t="n">
+        <v>-0.4479352888831881</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H222"/>
+  <dimension ref="A1:H223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6184,6 +6184,32 @@
         <v>-0.4479352888831881</v>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B223" t="n">
+        <v>328000</v>
+      </c>
+      <c r="C223" t="n">
+        <v>16429</v>
+      </c>
+      <c r="D223" t="n">
+        <v>362314</v>
+      </c>
+      <c r="E223" t="n">
+        <v>340909</v>
+      </c>
+      <c r="F223" t="n">
+        <v>335236</v>
+      </c>
+      <c r="G223" t="n">
+        <v>346153</v>
+      </c>
+      <c r="H223" t="n">
+        <v>-0.4449963523837773</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H223"/>
+  <dimension ref="A1:H224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6210,6 +6210,32 @@
         <v>-0.4449963523837773</v>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B224" t="n">
+        <v>332000</v>
+      </c>
+      <c r="C224" t="n">
+        <v>21073</v>
+      </c>
+      <c r="D224" t="n">
+        <v>362032</v>
+      </c>
+      <c r="E224" t="n">
+        <v>341006</v>
+      </c>
+      <c r="F224" t="n">
+        <v>336346</v>
+      </c>
+      <c r="G224" t="n">
+        <v>346462</v>
+      </c>
+      <c r="H224" t="n">
+        <v>-0.4445009179166098</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H224"/>
+  <dimension ref="A1:H225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6236,6 +6236,32 @@
         <v>-0.4445009179166098</v>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B225" t="n">
+        <v>317500</v>
+      </c>
+      <c r="C225" t="n">
+        <v>22167</v>
+      </c>
+      <c r="D225" t="n">
+        <v>360863</v>
+      </c>
+      <c r="E225" t="n">
+        <v>340233</v>
+      </c>
+      <c r="F225" t="n">
+        <v>328696</v>
+      </c>
+      <c r="G225" t="n">
+        <v>343264</v>
+      </c>
+      <c r="H225" t="n">
+        <v>-0.4496284241496245</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:H226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6262,6 +6262,32 @@
         <v>-0.4496284241496245</v>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B226" t="n">
+        <v>312000</v>
+      </c>
+      <c r="C226" t="n">
+        <v>24030</v>
+      </c>
+      <c r="D226" t="n">
+        <v>359826</v>
+      </c>
+      <c r="E226" t="n">
+        <v>339262</v>
+      </c>
+      <c r="F226" t="n">
+        <v>325055</v>
+      </c>
+      <c r="G226" t="n">
+        <v>341381</v>
+      </c>
+      <c r="H226" t="n">
+        <v>-0.4526475280385445</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H226"/>
+  <dimension ref="A1:H227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6288,6 +6288,32 @@
         <v>-0.4526475280385445</v>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B227" t="n">
+        <v>316500</v>
+      </c>
+      <c r="C227" t="n">
+        <v>26282</v>
+      </c>
+      <c r="D227" t="n">
+        <v>358853</v>
+      </c>
+      <c r="E227" t="n">
+        <v>338674</v>
+      </c>
+      <c r="F227" t="n">
+        <v>320406</v>
+      </c>
+      <c r="G227" t="n">
+        <v>339311</v>
+      </c>
+      <c r="H227" t="n">
+        <v>-0.4559664579642293</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H227"/>
+  <dimension ref="A1:H228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6314,6 +6314,32 @@
         <v>-0.4559664579642293</v>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B228" t="n">
+        <v>307000</v>
+      </c>
+      <c r="C228" t="n">
+        <v>37550</v>
+      </c>
+      <c r="D228" t="n">
+        <v>357937</v>
+      </c>
+      <c r="E228" t="n">
+        <v>336934</v>
+      </c>
+      <c r="F228" t="n">
+        <v>315615</v>
+      </c>
+      <c r="G228" t="n">
+        <v>336828</v>
+      </c>
+      <c r="H228" t="n">
+        <v>-0.4599475705272609</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에피스홀딩스_일별_기준주가.xlsx
+++ b/data/삼성에피스홀딩스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H228"/>
+  <dimension ref="A1:H229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6340,6 +6340,32 @@
         <v>-0.4599475705272609</v>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B229" t="n">
+        <v>309500</v>
+      </c>
+      <c r="C229" t="n">
+        <v>26571</v>
+      </c>
+      <c r="D229" t="n">
+        <v>357338</v>
+      </c>
+      <c r="E229" t="n">
+        <v>335265</v>
+      </c>
+      <c r="F229" t="n">
+        <v>311898</v>
+      </c>
+      <c r="G229" t="n">
+        <v>334833</v>
+      </c>
+      <c r="H229" t="n">
+        <v>-0.4631462493686818</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
